--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J155-MethodGlucoseSanguin-ENS.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J155-MethodGlucoseSanguin-ENS.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -116,9 +116,6 @@
   </si>
   <si>
     <t>82078001</t>
-  </si>
-  <si>
-    <t>prélèvement d'un échantillon sanguin pour le laboratoire</t>
   </si>
   <si>
     <t>http://snomed.info/sct</t>
@@ -448,9 +445,7 @@
       <c r="A2" t="s" s="2">
         <v>33</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>34</v>
-      </c>
+      <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -465,7 +460,7 @@
         <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
